--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLAMENTO - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLAMENTO - 27_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6203</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>36</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +482,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +507,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +532,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +557,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -558,7 +578,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -579,7 +603,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -600,7 +628,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -621,7 +653,11 @@
           <t>21</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -642,7 +678,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -663,7 +703,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -697,7 +741,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -743,7 +791,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -764,7 +816,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -785,7 +841,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -819,7 +879,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -840,7 +904,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -861,7 +929,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -882,7 +954,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -903,7 +979,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -924,7 +1004,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -945,7 +1029,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -966,7 +1054,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -987,7 +1079,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1025,7 +1121,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1046,7 +1146,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1067,7 +1171,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1088,7 +1196,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1109,7 +1221,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1130,7 +1246,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1151,7 +1271,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1189,7 +1313,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1210,7 +1338,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1231,7 +1363,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1252,7 +1388,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1273,7 +1413,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1294,7 +1438,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1315,7 +1463,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1336,7 +1488,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1357,7 +1513,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1378,7 +1538,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1399,7 +1563,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1420,7 +1588,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1466,7 +1638,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1554,7 +1730,61 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>72</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7899258708553</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ROLAMENTO PARA MOTOR NACHI VIRABREQUIM 35BC0755NC2C518</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>73</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7899258706191</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ROLAMENTO MOTOR NACHI VIRABREQUIM   35BC07558</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLAMENTO - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLAMENTO - 27_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,17 +444,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>ROLAMENTO NACHI 6203 320895</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
     </row>
@@ -482,11 +472,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -554,12 +529,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -578,11 +548,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -603,1186 +568,1104 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7899258703190</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ROLAMENTO NACHI 6301</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7895099126181</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ROLAMENTO IRON 6004 046107</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7898520247974</t>
+          <t>7899258703190</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ROLAMENTO SCUD 6004 10380002</t>
+          <t>ROLAMENTO NACHI 6301</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7908217206198</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ROLAMENTO PMKE 6004</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>7895099126181</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ROLAMENTO IRON 6004 046107</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7899258700076</t>
+          <t>7898520247974</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6000</t>
+          <t>ROLAMENTO SCUD 6004 10380002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7895099126327</t>
+          <t>7908217206198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROLAMENTO IRON 6303 046089</t>
+          <t>ROLAMENTO PMKE 6004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7899258703480</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ROLAMENTO NACHI 6303</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7898520248025</t>
+          <t>7899258700076</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ROLAMENTO SCUD 6303 10380015</t>
+          <t>ROLAMENTO NACHI 6000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7895099126310</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ROLAMENTO IRON 6302 046088</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>7895099126327</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ROLAMENTO IRON 6303 046089</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7909201067221</t>
+          <t>7899258703480</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ROLAMENTO WW3 6003 1106030</t>
+          <t>ROLAMENTO NACHI 6303</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7899258701844</t>
+          <t>7898520248025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6202</t>
+          <t>ROLAMENTO SCUD 6303 10380015</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>25</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>7899258701554</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ROLAMENTO NACHI 6202</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7899248112711</t>
+          <t>7895099126310</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ROLAMENTO WW3 6202 1101833</t>
+          <t>ROLAMENTO IRON 6302 046088</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7895099126204</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>ROLAMENTO IRON 6202 046111</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7909201028925</t>
+          <t>7909201067221</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ROLAMENTO WW3 6204 1102288</t>
+          <t>ROLAMENTO WW3 6003 1106030</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7899651862067</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ROLAMENTO SCUD 6204 10380019</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>69438575000</t>
+          <t>7899258701844</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROLAMENTO RT 6204 </t>
+          <t>ROLAMENTO NACHI 6202</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7316575092580</t>
+          <t>7899258701554</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ROLAMENTO SKF 6204 6204-2Z</t>
+          <t>ROLAMENTO NACHI 6202</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>33</v>
-      </c>
-      <c r="B29" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7899248112711</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROLAMENTO FAG 6204 </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>ROLAMENTO WW3 6202 1101833</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7899258704852</t>
+          <t>7895099126204</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6205 3183502</t>
+          <t>ROLAMENTO IRON 6202 046111</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>36</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>7316576733567</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ROLAMENTO SKF 6205 6205-2RSH</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7899153232030</t>
+          <t>7909201028925</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROLAMENTO GTOP 6300 </t>
+          <t>ROLAMENTO WW3 6204 1102288</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>69438574000</t>
+          <t>7899651862067</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ROLAMENTO RT 6201</t>
+          <t>ROLAMENTO SCUD 6204 10380019</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7316575080655</t>
+          <t>69438575000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ROLAMENTO SKF 6201 6201-2Z</t>
+          <t xml:space="preserve">ROLAMENTO RT 6204 </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7899651804043</t>
+          <t>7316575092580</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ROLAMENTO SCUD 6201 10380018</t>
+          <t>ROLAMENTO SKF 6204 6204-2Z</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>43</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>7895099126198</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ROLAMENTO IRON 6201 046109</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ROLAMENTO FAG 6204 </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>44</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7909201067214</t>
+          <t>7899258704852</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ROLAMENTO WW3 6001 1106029</t>
+          <t>ROLAMENTO NACHI 6205 3183502</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3800000018312</t>
+          <t>7316576733567</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ROLAMENTO SOLIDEZ 6001 38000</t>
+          <t>ROLAMENTO SKF 6205 6205-2RSH</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>47</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>7895099126174</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ROLAMENTO IRON 6001 046106</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7899258700212</t>
+          <t>7899153232030</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6001</t>
+          <t xml:space="preserve">ROLAMENTO GTOP 6300 </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>51</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>7895099126334</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ROLAMENTO IRON 6304 046093</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7899258703572</t>
+          <t>69438574000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6304</t>
+          <t>ROLAMENTO RT 6201</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7899258700441</t>
+          <t>7316575080655</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6002</t>
+          <t>ROLAMENTO SKF 6201 6201-2Z</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7899651871946</t>
+          <t>7899651804043</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ROLAMENTO SCUD 6002 10380024</t>
+          <t>ROLAMENTO SCUD 6201 10380018</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>70341179130</t>
+          <t>7895099126198</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ROLAMENTO IRON 6902 187262</t>
+          <t>ROLAMENTO IRON 6201 046109</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>602883763852</t>
+          <t> </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ROLAMENTO IRON 6905 187261</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>602883763869</t>
+          <t>7909201067214</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ROLAMENTO (ÁRVORE COMANDO) IRON 6904 187263</t>
+          <t>ROLAMENTO WW3 6001 1106029</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7899258708485</t>
+          <t>3800000018312</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 6006</t>
+          <t>ROLAMENTO SOLIDEZ 6001 38000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>48</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>751320982261</t>
+          <t>7895099126174</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ROLAMENTO IRON 6007</t>
+          <t>ROLAMENTO IRON 6001 046106</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7899258708843</t>
+          <t>7899258700212</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 63/22</t>
+          <t>ROLAMENTO NACHI 6001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>78</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>66</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7899258703107</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ROLAMENTO NACHI 63/28</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7899258703121</t>
+          <t>7895099126334</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI 63/28</t>
+          <t>ROLAMENTO IRON 6304 046093</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>115</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7899258700021</t>
+          <t>7899258703572</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ROLAMENTO NACHI VIRABREQUIM</t>
+          <t>ROLAMENTO NACHI 6304</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>125</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>72</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>7899258708553</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ROLAMENTO PARA MOTOR NACHI VIRABREQUIM 35BC0755NC2C518</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7899258700441</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ROLAMENTO NACHI 6002</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7899651871946</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ROLAMENTO SCUD 6002 10380024</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>70341179130</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ROLAMENTO IRON 6902 187262</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>602883763852</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ROLAMENTO IRON 6905 187261</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>602883763869</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ROLAMENTO (ÁRVORE COMANDO) IRON 6904 187263</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7899258708485</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ROLAMENTO NACHI 6006</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>751320982261</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ROLAMENTO IRON 6007</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7899258708843</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ROLAMENTO NACHI 63/22</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>7899258703107</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ROLAMENTO NACHI 63/28</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7899258703121</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ROLAMENTO NACHI 63/28</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7899258700021</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ROLAMENTO NACHI VIRABREQUIM</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7899258708553</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ROLAMENTO PARA MOTOR NACHI VIRABREQUIM 35BC0755NC2C518</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>7899258706191</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>ROLAMENTO MOTOR NACHI VIRABREQUIM   35BC07558</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>160</t>
         </is>
       </c>
     </row>
